--- a/numerical-workflows/v2/framework/06_最终配置/任务/TaskTarget.xlsx
+++ b/numerical-workflows/v2/framework/06_最终配置/任务/TaskTarget.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="TaskTarget" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="钓鱼" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TaskTarget" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="钓鱼" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C175" s="40" t="inlineStr">
         <is>
-          <t>1个舱室达到2级</t>
+          <t>2个舱室达到2级</t>
         </is>
       </c>
       <c r="D175" s="54" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>2,1</t>
+          <t>2,2</t>
         </is>
       </c>
       <c r="F175" s="0" t="n"/>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="C185" s="40" t="inlineStr">
         <is>
-          <t>2个舱室达到2级</t>
+          <t>3个舱室达到2级</t>
         </is>
       </c>
       <c r="D185" s="45" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="E185" s="46" t="inlineStr">
         <is>
-          <t>2,2</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="F185" s="54" t="n"/>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="C193" s="40" t="inlineStr">
         <is>
-          <t>1个舱室达到3级</t>
+          <t>2个舱室达到3级</t>
         </is>
       </c>
       <c r="D193" s="54" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="E193" s="44" t="inlineStr">
         <is>
-          <t>3,1</t>
+          <t>3,2</t>
         </is>
       </c>
       <c r="F193" s="54" t="n"/>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="C202" s="40" t="inlineStr">
         <is>
-          <t>2个舱室达到3级</t>
+          <t>3个舱室达到3级</t>
         </is>
       </c>
       <c r="D202" s="45" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="E202" s="46" t="inlineStr">
         <is>
-          <t>3,2</t>
+          <t>3,3</t>
         </is>
       </c>
       <c r="F202" s="54" t="n"/>
@@ -8203,17 +8203,17 @@
       </c>
       <c r="C249" s="55" t="inlineStr">
         <is>
-          <t>累计击败BOSS敌人3个</t>
+          <t>加一个好友</t>
         </is>
       </c>
       <c r="D249" s="54" t="inlineStr">
         <is>
-          <t>Target_TTT_BossMonster_Kill_Times</t>
+          <t>Target_TTT_Friends_AddTimes</t>
         </is>
       </c>
       <c r="E249" s="56" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="F249" s="0" t="n"/>
@@ -8222,7 +8222,7 @@
         <v>0</v>
       </c>
       <c r="I249" s="0" t="n">
-        <v>204</v>
+        <v>2</v>
       </c>
       <c r="J249" s="0" t="n"/>
     </row>
